--- a/Assets/SandPlanet/Data/Authoring/SandPlanet_Master.xlsx
+++ b/Assets/SandPlanet/Data/Authoring/SandPlanet_Master.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_작성 가이드" sheetId="1" r:id="R7a1c9d0b888543d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_장소" sheetId="2" r:id="R9a80f548b22b442d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_캐릭터" sheetId="3" r:id="R5450ed37ce2a420e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_사물·상호작용 대상" sheetId="4" r:id="Rb0055cbe12be4781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_퀘스트" sheetId="5" r:id="Rd7216e42c2c64121"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_퀘스트 단계" sheetId="6" r:id="Rcef9f70a376f4eba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_상호작용 플로우" sheetId="7" r:id="R8fd0ea53dfc34614"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_상태·플래그" sheetId="9" r:id="R65a97868253d4e53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_이벤트 플로우" sheetId="10" r:id="R5de5173f6c8a4ebd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_이벤트 트리거" sheetId="11" r:id="R0cede75a776a4176"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_NPC 일정" sheetId="12" r:id="R36bfbe3f40e74321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_코드" sheetId="13" r:id="Re29aa8e4e27c4d53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참고_3주 콘텐츠 맵" sheetId="14" r:id="R2f0b942c6c10486f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참고_퀘스트 흐름" sheetId="15" r:id="R3ebb8b1b857b45b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발_Importer 검증_v1.4" sheetId="16" r:id="R5d7df5704ec449a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발_v1.6 전환 체크" sheetId="19" r:id="R8bfd1485e98d4068"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_작성 가이드" sheetId="1" r:id="Re2bb3a9eb8ed4714"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_장소" sheetId="2" r:id="R203debd64e984f01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_캐릭터" sheetId="3" r:id="R1f6313ddb64747d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_사물·상호작용 대상" sheetId="4" r:id="R64a3e5a2af414cf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_퀘스트" sheetId="5" r:id="R99b85d0ec4cb4dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_퀘스트 단계" sheetId="6" r:id="R55b465d4652f454d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_상호작용 플로우" sheetId="7" r:id="R2319ae7b74504585"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_상태·플래그" sheetId="9" r:id="R2da0564fc64344ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_이벤트 플로우" sheetId="10" r:id="Rf1e4aba757d442f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_이벤트 트리거" sheetId="11" r:id="R225041e7df0842bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_NPC 일정" sheetId="12" r:id="Reac68ee8516b4a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_코드" sheetId="13" r:id="R037ed6e947984cc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참고_3주 콘텐츠 맵" sheetId="14" r:id="R494c52dbd2db4b81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="참고_퀘스트 흐름" sheetId="15" r:id="R6e6f2c70c52a4d05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발_Importer 검증_v1.4" sheetId="16" r:id="R3c8674240b084720"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개발_v1.6 전환 체크" sheetId="19" r:id="R3d90b9a197ad442e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -24010,14 +24010,14 @@
         <x:v>CHA_BENJAMIN</x:v>
       </x:c>
       <x:c r="M10" s="504" t="str">
-        <x:v>벤자민은 대답 대신 묘지 쪽을 본다. 잠시 뒤, “네가 깨어난 날에 이런 얘기까지 해야 하나 싶네.”라고 낮게 말한다.</x:v>
+        <x:v>벤자민은 말을 하다 말고 묘지 쪽을 본다. 잠깐 뒤 낮게 말한다. “나중에 시간 되면 같이 가줄래?”</x:v>
       </x:c>
       <x:c r="N10" s="504" t="str">
-        <x:v>그래도 네가 원할 때 같이 가자.</x:v>
+        <x:v>지금 가자.</x:v>
       </x:c>
       <x:c r="O10" s="504"/>
       <x:c r="P10" s="504" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q10" s="504" t="n">
         <x:v>0</x:v>
@@ -24099,7 +24099,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="BF10" s="504" t="str">
-        <x:v>W1 캐릭터 퀘스트 OFFER. 해당 인물과 Main 재회 후 노출.</x:v>
+        <x:v>D1 Narrative v1.8: 묘지 Character Quest의 OFFER는 초대만 담당. 실제 시간/관계 결과는 진행 장면에서 처리.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="40" customHeight="1">
@@ -27742,13 +27742,13 @@
         <x:v>N01</x:v>
       </x:c>
       <x:c r="C42" s="504" t="str">
-        <x:v>CHO_W1_BEN_NAMES</x:v>
+        <x:v>CHO_W1_BEN_NAMES_COUNT</x:v>
       </x:c>
       <x:c r="D42" s="504" t="str">
         <x:v>CHA_BENJAMIN</x:v>
       </x:c>
       <x:c r="E42" s="504" t="str">
-        <x:v>묘지를 함께 걷자고 말한다</x:v>
+        <x:v>묘지에 같이 간다</x:v>
       </x:c>
       <x:c r="F42" s="504" t="str">
         <x:v>QST_CHAR_BENJAMIN</x:v>
@@ -27768,16 +27768,17 @@
         <x:v>NARRATOR</x:v>
       </x:c>
       <x:c r="M42" s="504" t="str">
-        <x:v>벤자민은 묘지 안쪽으로 천천히 걷는다. 제이는 그가 유난히 오래 머무는 두 개의 묘비를 발견한다.</x:v>
+        <x:v>묘지는 정착지에서 멀지 않았다.
+정리된 돌무더기마다 이름이 하나씩 적혀 있었다.</x:v>
       </x:c>
       <x:c r="N42" s="504" t="str">
-        <x:v>두 사람은 누구야?</x:v>
+        <x:v>이렇게 많았어?</x:v>
       </x:c>
       <x:c r="O42" s="504" t="str">
         <x:v>N02</x:v>
       </x:c>
       <x:c r="P42" s="504" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="Q42" s="504" t="n">
         <x:v>0</x:v>
@@ -27786,7 +27787,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="S42" s="504" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="T42" s="504" t="n">
         <x:v>0</x:v>
@@ -27851,7 +27852,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="BF42" s="504" t="str">
-        <x:v>Day1부터 진행 가능. 한 번의 추모로 상실을 해결하지 않는다.</x:v>
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="40" customHeight="1">
@@ -27861,12 +27862,14 @@
       <x:c r="B43" s="504" t="str">
         <x:v>N02</x:v>
       </x:c>
-      <x:c r="C43" s="504"/>
+      <x:c r="C43" s="504" t="str">
+        <x:v>CHO_W1_BEN_NAMES_TWO_GRAVES</x:v>
+      </x:c>
       <x:c r="D43" s="504" t="str">
         <x:v>CHA_BENJAMIN</x:v>
       </x:c>
       <x:c r="E43" s="504" t="str">
-        <x:v>묘지를 함께 걷자고 말한다</x:v>
+        <x:v>묘지에 같이 간다</x:v>
       </x:c>
       <x:c r="F43" s="504" t="str">
         <x:v>QST_CHAR_BENJAMIN</x:v>
@@ -27886,32 +27889,38 @@
         <x:v>CHA_BENJAMIN</x:v>
       </x:c>
       <x:c r="M43" s="504" t="str">
-        <x:v>벤자민은 한참 뒤에야 이름을 말한다. “내 아내와 아이야. 착륙할 때 둘 다 죽었어.” 그는 제이를 보지 않은 채 묘비의 모래만 털어낸다.</x:v>
+        <x:v>첫날에 많이 죽었지.</x:v>
       </x:c>
       <x:c r="N43" s="504" t="str">
-        <x:v>말없이 옆에 남는다.</x:v>
-      </x:c>
-      <x:c r="O43" s="504"/>
-      <x:c r="P43" s="504"/>
-      <x:c r="Q43" s="504"/>
-      <x:c r="R43" s="504"/>
-      <x:c r="S43" s="504"/>
-      <x:c r="T43" s="504"/>
-      <x:c r="U43" s="504" t="str">
-        <x:v>CHA_BENJAMIN</x:v>
-      </x:c>
-      <x:c r="V43" s="504" t="n">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>벤자민 앞에 놓인 두 개의 무덤을 바라본다.</x:v>
+      </x:c>
+      <x:c r="O43" s="504" t="str">
+        <x:v>N03</x:v>
+      </x:c>
+      <x:c r="P43" s="504" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q43" s="504" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R43" s="504" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S43" s="504" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T43" s="504" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U43" s="504"/>
+      <x:c r="V43" s="504"/>
       <x:c r="W43" s="504"/>
       <x:c r="X43" s="504"/>
       <x:c r="Y43" s="504"/>
       <x:c r="Z43" s="504"/>
       <x:c r="AA43" s="504"/>
       <x:c r="AB43" s="504"/>
-      <x:c r="AC43" s="504" t="str">
-        <x:v>EVT_W1_BEN_NAMES_DONE</x:v>
-      </x:c>
+      <x:c r="AC43" s="504"/>
       <x:c r="AD43" s="504"/>
       <x:c r="AE43" s="504" t="str">
         <x:v>MENU_OPTION</x:v>
@@ -27942,9 +27951,15 @@
       <x:c r="AQ43" s="504"/>
       <x:c r="AR43" s="504"/>
       <x:c r="AS43" s="504"/>
-      <x:c r="AT43" s="504"/>
-      <x:c r="AU43" s="504"/>
-      <x:c r="AV43" s="504"/>
+      <x:c r="AT43" s="504" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU43" s="504" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV43" s="504" t="str">
+        <x:v>AND</x:v>
+      </x:c>
       <x:c r="AW43" s="504"/>
       <x:c r="AX43" s="504"/>
       <x:c r="AY43" s="504"/>
@@ -27956,7 +27971,9 @@
       <x:c r="BE43" s="518" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="BF43" s="504"/>
+      <x:c r="BF43" s="504" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
     </x:row>
     <x:row r="44" ht="40" customHeight="1">
       <x:c r="A44" s="504" t="str">
@@ -36507,7 +36524,9 @@
       <x:c r="B110" t="str">
         <x:v>N01</x:v>
       </x:c>
-      <x:c r="C110"/>
+      <x:c r="C110" t="str">
+        <x:v>CHO_W1_BOR_WEATHER</x:v>
+      </x:c>
       <x:c r="D110" t="str">
         <x:v>CHA_BORICHI</x:v>
       </x:c>
@@ -36526,18 +36545,20 @@
       <x:c r="I110"/>
       <x:c r="J110"/>
       <x:c r="K110" t="str">
-        <x:v>DIALOGUE</x:v>
+        <x:v>NARRATION</x:v>
       </x:c>
       <x:c r="L110" t="str">
-        <x:v>CHA_BORICHI</x:v>
+        <x:v>NARRATOR</x:v>
       </x:c>
       <x:c r="M110" t="str">
-        <x:v>보리치는 짧게 안부를 묻고 바로 관측 기록을 접어 든다. “오늘 바람이 조금 틀어졌어. 큰 차이는 아닌데… 작은 차이를 놓치면 사람이 죽으니까.”</x:v>
+        <x:v>보리치는 짧게 안부를 묻고 바로 관측 기록을 접어 든다.</x:v>
       </x:c>
       <x:c r="N110" t="str">
-        <x:v>여전히 기록을 전부 보고 있구나.</x:v>
-      </x:c>
-      <x:c r="O110"/>
+        <x:v>오늘 바람은 어때?</x:v>
+      </x:c>
+      <x:c r="O110" t="str">
+        <x:v>N02</x:v>
+      </x:c>
       <x:c r="P110" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -36614,7 +36635,9 @@
       <x:c r="AU110" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV110"/>
+      <x:c r="AV110" t="str">
+        <x:v>AND</x:v>
+      </x:c>
       <x:c r="AW110"/>
       <x:c r="AX110"/>
       <x:c r="AY110"/>
@@ -36627,7 +36650,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="BF110" t="str">
-        <x:v>Day1~2 도입 Main. 과로/생존자 죄책감을 직접 설명하지 않고 관측 집착으로 암시.</x:v>
+        <x:v>Narrative UX v1.9: 내레이션과 인물 대사를 같은 BodyText에 섞지 않음.</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -36637,12 +36660,14 @@
       <x:c r="B111" t="str">
         <x:v>N01</x:v>
       </x:c>
-      <x:c r="C111"/>
+      <x:c r="C111" t="str">
+        <x:v>CHO_W1_DIYA_WALK</x:v>
+      </x:c>
       <x:c r="D111" t="str">
         <x:v>CHA_DIYA</x:v>
       </x:c>
       <x:c r="E111" t="str">
-        <x:v>디야와 거주지를 한 바퀴 걷는다</x:v>
+        <x:v>거주지의 변화를 묻는다</x:v>
       </x:c>
       <x:c r="F111" t="str">
         <x:v>QST_W1_MAIN_01_AWAKE</x:v>
@@ -36656,18 +36681,20 @@
       <x:c r="I111"/>
       <x:c r="J111"/>
       <x:c r="K111" t="str">
-        <x:v>DIALOGUE</x:v>
+        <x:v>NARRATION</x:v>
       </x:c>
       <x:c r="L111" t="str">
-        <x:v>CHA_DIYA</x:v>
+        <x:v>NARRATOR</x:v>
       </x:c>
       <x:c r="M111" t="str">
-        <x:v>디야는 제이가 기억하는 임시 텐트 자리를 가리킨다. 그곳에는 덧댄 벽, 말린 옷, 아이가 그린 표식이 남아 있다. “네가 잠든 사이 임시라는 말이 조금씩 거짓말이 됐어.”</x:v>
+        <x:v>디야는 제이가 기억하는 임시 텐트 자리를 가리킨다.</x:v>
       </x:c>
       <x:c r="N111" t="str">
-        <x:v>여길 집처럼 쓰고 있구나.</x:v>
-      </x:c>
-      <x:c r="O111"/>
+        <x:v>디야와 거주지를 한 바퀴 걷는다.</x:v>
+      </x:c>
+      <x:c r="O111" t="str">
+        <x:v>N02</x:v>
+      </x:c>
       <x:c r="P111" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -36744,7 +36771,9 @@
       <x:c r="AU111" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AV111"/>
+      <x:c r="AV111" t="str">
+        <x:v>AND</x:v>
+      </x:c>
       <x:c r="AW111"/>
       <x:c r="AX111"/>
       <x:c r="AY111"/>
@@ -36757,7 +36786,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="BF111" t="str">
-        <x:v>Day1~2 도입 Main. 정착 관점을 설명 대신 생활 흔적으로 제시.</x:v>
+        <x:v>Narrative UX v1.9: 행동 선택에 시간비용 부여. 내레이션과 대사 Beat 분리.</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -39308,6 +39337,2477 @@
       </x:c>
       <x:c r="BF133" t="str">
         <x:v>제한 공개 분기 종료.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>N03</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>CHO_W1_BEN_NAMES_WALK</x:v>
+      </x:c>
+      <x:c r="D134" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E134" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F134" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G134" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H134" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I134"/>
+      <x:c r="J134"/>
+      <x:c r="K134" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="L134" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="M134" t="str">
+        <x:v>여긴 내 아내. 옆은 내 아이.</x:v>
+      </x:c>
+      <x:c r="N134" t="str">
+        <x:v>잠시 함께 걷는다.</x:v>
+      </x:c>
+      <x:c r="O134" t="str">
+        <x:v>A01</x:v>
+      </x:c>
+      <x:c r="P134" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="Q134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U134" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="V134" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W134"/>
+      <x:c r="X134"/>
+      <x:c r="Y134"/>
+      <x:c r="Z134"/>
+      <x:c r="AA134"/>
+      <x:c r="AB134"/>
+      <x:c r="AC134" t="str">
+        <x:v>EVT_W1_BEN_NAMES_DONE</x:v>
+      </x:c>
+      <x:c r="AD134"/>
+      <x:c r="AE134" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF134" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG134" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH134" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI134" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ134" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK134" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL134"/>
+      <x:c r="AM134"/>
+      <x:c r="AN134"/>
+      <x:c r="AO134"/>
+      <x:c r="AP134"/>
+      <x:c r="AQ134"/>
+      <x:c r="AR134"/>
+      <x:c r="AS134"/>
+      <x:c r="AT134" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU134" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV134" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW134"/>
+      <x:c r="AX134"/>
+      <x:c r="AY134"/>
+      <x:c r="AZ134"/>
+      <x:c r="BA134"/>
+      <x:c r="BB134"/>
+      <x:c r="BC134"/>
+      <x:c r="BD134"/>
+      <x:c r="BE134" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF134" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>N03</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>CHO_W1_BEN_NAMES_RETURN</x:v>
+      </x:c>
+      <x:c r="D135" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E135" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F135" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G135" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H135" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I135"/>
+      <x:c r="J135"/>
+      <x:c r="K135" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="L135" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="M135" t="str">
+        <x:v>여긴 내 아내. 옆은 내 아이.</x:v>
+      </x:c>
+      <x:c r="N135" t="str">
+        <x:v>다음에 다시 와도 될까?</x:v>
+      </x:c>
+      <x:c r="O135" t="str">
+        <x:v>B01</x:v>
+      </x:c>
+      <x:c r="P135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U135" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="V135" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="W135"/>
+      <x:c r="X135"/>
+      <x:c r="Y135"/>
+      <x:c r="Z135"/>
+      <x:c r="AA135"/>
+      <x:c r="AB135"/>
+      <x:c r="AC135" t="str">
+        <x:v>EVT_W1_BEN_NAMES_DONE</x:v>
+      </x:c>
+      <x:c r="AD135"/>
+      <x:c r="AE135" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF135" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG135" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH135" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI135" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ135" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK135" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL135"/>
+      <x:c r="AM135"/>
+      <x:c r="AN135"/>
+      <x:c r="AO135"/>
+      <x:c r="AP135"/>
+      <x:c r="AQ135"/>
+      <x:c r="AR135"/>
+      <x:c r="AS135"/>
+      <x:c r="AT135" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU135" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV135" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW135"/>
+      <x:c r="AX135"/>
+      <x:c r="AY135"/>
+      <x:c r="AZ135"/>
+      <x:c r="BA135"/>
+      <x:c r="BB135"/>
+      <x:c r="BC135"/>
+      <x:c r="BD135"/>
+      <x:c r="BE135" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF135" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>N03</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>CHO_W1_BEN_NAMES_LEAVE</x:v>
+      </x:c>
+      <x:c r="D136" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E136" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F136" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G136" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H136" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I136"/>
+      <x:c r="J136"/>
+      <x:c r="K136" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="L136" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="M136" t="str">
+        <x:v>여긴 내 아내. 옆은 내 아이.</x:v>
+      </x:c>
+      <x:c r="N136" t="str">
+        <x:v>이제 돌아가자고 말한다.</x:v>
+      </x:c>
+      <x:c r="O136" t="str">
+        <x:v>C01</x:v>
+      </x:c>
+      <x:c r="P136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U136"/>
+      <x:c r="V136"/>
+      <x:c r="W136"/>
+      <x:c r="X136"/>
+      <x:c r="Y136"/>
+      <x:c r="Z136"/>
+      <x:c r="AA136"/>
+      <x:c r="AB136"/>
+      <x:c r="AC136" t="str">
+        <x:v>EVT_W1_BEN_NAMES_DONE</x:v>
+      </x:c>
+      <x:c r="AD136"/>
+      <x:c r="AE136" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF136" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG136" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH136" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI136" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ136" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK136" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL136"/>
+      <x:c r="AM136"/>
+      <x:c r="AN136"/>
+      <x:c r="AO136"/>
+      <x:c r="AP136"/>
+      <x:c r="AQ136"/>
+      <x:c r="AR136"/>
+      <x:c r="AS136"/>
+      <x:c r="AT136" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU136" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV136" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW136"/>
+      <x:c r="AX136"/>
+      <x:c r="AY136"/>
+      <x:c r="AZ136"/>
+      <x:c r="BA136"/>
+      <x:c r="BB136"/>
+      <x:c r="BC136"/>
+      <x:c r="BD136"/>
+      <x:c r="BE136" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF136" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>A01</x:v>
+      </x:c>
+      <x:c r="C137"/>
+      <x:c r="D137" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E137" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F137" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G137" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H137" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I137"/>
+      <x:c r="J137"/>
+      <x:c r="K137" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L137" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M137" t="str">
+        <x:v>제이는 이름을 하나씩 읽었다.
+벤자민은 가족 이야기를 길게 하지 않았다. 아이가 매운 음식을 못 먹었다는 것, 아내가 출항 전날까지 짐을 다시 쌌다는 것 같은 이야기만 했다.
+돌아갈 때가 되자 벤자민이 먼저 입을 열었다.</x:v>
+      </x:c>
+      <x:c r="N137" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O137" t="str">
+        <x:v>A02</x:v>
+      </x:c>
+      <x:c r="P137"/>
+      <x:c r="Q137"/>
+      <x:c r="R137"/>
+      <x:c r="S137"/>
+      <x:c r="T137"/>
+      <x:c r="U137"/>
+      <x:c r="V137"/>
+      <x:c r="W137"/>
+      <x:c r="X137"/>
+      <x:c r="Y137"/>
+      <x:c r="Z137"/>
+      <x:c r="AA137"/>
+      <x:c r="AB137"/>
+      <x:c r="AC137"/>
+      <x:c r="AD137"/>
+      <x:c r="AE137" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF137" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG137" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH137" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI137" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ137" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK137" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL137"/>
+      <x:c r="AM137"/>
+      <x:c r="AN137"/>
+      <x:c r="AO137"/>
+      <x:c r="AP137"/>
+      <x:c r="AQ137"/>
+      <x:c r="AR137"/>
+      <x:c r="AS137"/>
+      <x:c r="AT137" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU137" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV137" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW137"/>
+      <x:c r="AX137"/>
+      <x:c r="AY137"/>
+      <x:c r="AZ137"/>
+      <x:c r="BA137"/>
+      <x:c r="BB137"/>
+      <x:c r="BC137"/>
+      <x:c r="BD137"/>
+      <x:c r="BE137" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF137" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>FLOW_W1_SHIP_OVERVIEW</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>N01</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>CHO_W1_SHIP_OVERVIEW_WALK</x:v>
+      </x:c>
+      <x:c r="D138" t="str">
+        <x:v>OBJ_02_SHIP_CONSOLE</x:v>
+      </x:c>
+      <x:c r="E138" t="str">
+        <x:v>수송선의 현재 상태를 처음부터 확인한다</x:v>
+      </x:c>
+      <x:c r="F138"/>
+      <x:c r="G138"/>
+      <x:c r="H138" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="I138"/>
+      <x:c r="J138"/>
+      <x:c r="K138" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L138" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M138" t="str">
+        <x:v>수송선은 멀리서 보면 아직 배였다.
+가까이 가면 생각이 조금 달라진다. 외벽은 군데군데 덧대어져 있고, 원래 문이었을 곳엔 철판이 박혀 있다. 모래는 착륙 장치 절반을 삼켰다.
+안쪽에서는 오래된 환풍기 소리가 일정하지 않은 박자로 끊긴다.</x:v>
+      </x:c>
+      <x:c r="N138" t="str">
+        <x:v>배 안을 한 바퀴 돌아본다.</x:v>
+      </x:c>
+      <x:c r="O138" t="str">
+        <x:v>A01</x:v>
+      </x:c>
+      <x:c r="P138" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U138"/>
+      <x:c r="V138"/>
+      <x:c r="W138"/>
+      <x:c r="X138"/>
+      <x:c r="Y138" t="str">
+        <x:v>STA_W1_SHIP_OVERVIEW_SEEN</x:v>
+      </x:c>
+      <x:c r="Z138" t="str">
+        <x:v>SET TRUE</x:v>
+      </x:c>
+      <x:c r="AA138"/>
+      <x:c r="AB138"/>
+      <x:c r="AC138"/>
+      <x:c r="AD138" t="str">
+        <x:v>수송선의 기본 상태를 확인했다.</x:v>
+      </x:c>
+      <x:c r="AE138" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF138" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG138" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH138" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI138" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ138" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="AK138" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL138"/>
+      <x:c r="AM138"/>
+      <x:c r="AN138"/>
+      <x:c r="AO138"/>
+      <x:c r="AP138"/>
+      <x:c r="AQ138"/>
+      <x:c r="AR138"/>
+      <x:c r="AS138"/>
+      <x:c r="AT138" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU138" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV138" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW138"/>
+      <x:c r="AX138"/>
+      <x:c r="AY138"/>
+      <x:c r="AZ138"/>
+      <x:c r="BA138"/>
+      <x:c r="BB138"/>
+      <x:c r="BC138"/>
+      <x:c r="BD138"/>
+      <x:c r="BE138" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF138" t="str">
+        <x:v>D1 Narrative v1.8: 비인물 소설식 상호작용. 수송선 기본 상태와 기술 잠금 선택 튜토리얼.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>FLOW_W1_SHIP_OVERVIEW</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>N01</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>CHO_W1_SHIP_OVERVIEW_DETAIL</x:v>
+      </x:c>
+      <x:c r="D139" t="str">
+        <x:v>OBJ_02_SHIP_CONSOLE</x:v>
+      </x:c>
+      <x:c r="E139" t="str">
+        <x:v>수송선의 현재 상태를 처음부터 확인한다</x:v>
+      </x:c>
+      <x:c r="F139"/>
+      <x:c r="G139"/>
+      <x:c r="H139" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="I139"/>
+      <x:c r="J139"/>
+      <x:c r="K139" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L139" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M139" t="str">
+        <x:v>수송선은 멀리서 보면 아직 배였다.
+가까이 가면 생각이 조금 달라진다. 외벽은 군데군데 덧대어져 있고, 원래 문이었을 곳엔 철판이 박혀 있다. 모래는 착륙 장치 절반을 삼켰다.
+안쪽에서는 오래된 환풍기 소리가 일정하지 않은 박자로 끊긴다.</x:v>
+      </x:c>
+      <x:c r="N139" t="str">
+        <x:v>손상 기록까지 확인한다.</x:v>
+      </x:c>
+      <x:c r="O139" t="str">
+        <x:v>B01</x:v>
+      </x:c>
+      <x:c r="P139" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q139" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R139" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S139" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T139" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U139"/>
+      <x:c r="V139"/>
+      <x:c r="W139"/>
+      <x:c r="X139"/>
+      <x:c r="Y139" t="str">
+        <x:v>STA_W1_SHIP_OVERVIEW_SEEN</x:v>
+      </x:c>
+      <x:c r="Z139" t="str">
+        <x:v>SET TRUE</x:v>
+      </x:c>
+      <x:c r="AA139" t="str">
+        <x:v>STA_W1_SHIP_DETAIL_SEEN</x:v>
+      </x:c>
+      <x:c r="AB139" t="str">
+        <x:v>SET TRUE</x:v>
+      </x:c>
+      <x:c r="AC139"/>
+      <x:c r="AD139" t="str">
+        <x:v>수송선의 손상 기록까지 확인했다.</x:v>
+      </x:c>
+      <x:c r="AE139" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF139" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG139" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH139" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI139" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ139" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="AK139" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL139"/>
+      <x:c r="AM139"/>
+      <x:c r="AN139"/>
+      <x:c r="AO139"/>
+      <x:c r="AP139"/>
+      <x:c r="AQ139"/>
+      <x:c r="AR139"/>
+      <x:c r="AS139"/>
+      <x:c r="AT139" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU139" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV139" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW139" t="str">
+        <x:v>STAT_LEVEL</x:v>
+      </x:c>
+      <x:c r="AX139" t="str">
+        <x:v>TECHNICAL</x:v>
+      </x:c>
+      <x:c r="AY139" t="str">
+        <x:v>GE</x:v>
+      </x:c>
+      <x:c r="AZ139" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="BA139"/>
+      <x:c r="BB139"/>
+      <x:c r="BC139"/>
+      <x:c r="BD139"/>
+      <x:c r="BE139" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF139" t="str">
+        <x:v>D1 Narrative v1.8: 비인물 소설식 상호작용. 수송선 기본 상태와 기술 잠금 선택 튜토리얼.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>FLOW_W1_SHIP_OVERVIEW</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>N01</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>CHO_W1_SHIP_OVERVIEW_LEAVE</x:v>
+      </x:c>
+      <x:c r="D140" t="str">
+        <x:v>OBJ_02_SHIP_CONSOLE</x:v>
+      </x:c>
+      <x:c r="E140" t="str">
+        <x:v>수송선의 현재 상태를 처음부터 확인한다</x:v>
+      </x:c>
+      <x:c r="F140"/>
+      <x:c r="G140"/>
+      <x:c r="H140" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="I140"/>
+      <x:c r="J140"/>
+      <x:c r="K140" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L140" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M140" t="str">
+        <x:v>수송선은 멀리서 보면 아직 배였다.
+가까이 가면 생각이 조금 달라진다. 외벽은 군데군데 덧대어져 있고, 원래 문이었을 곳엔 철판이 박혀 있다. 모래는 착륙 장치 절반을 삼켰다.
+안쪽에서는 오래된 환풍기 소리가 일정하지 않은 박자로 끊긴다.</x:v>
+      </x:c>
+      <x:c r="N140" t="str">
+        <x:v>오늘은 여기까지만 본다.</x:v>
+      </x:c>
+      <x:c r="O140" t="str">
+        <x:v>C01</x:v>
+      </x:c>
+      <x:c r="P140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U140"/>
+      <x:c r="V140"/>
+      <x:c r="W140"/>
+      <x:c r="X140"/>
+      <x:c r="Y140" t="str">
+        <x:v>STA_W1_SHIP_OVERVIEW_SEEN</x:v>
+      </x:c>
+      <x:c r="Z140" t="str">
+        <x:v>SET TRUE</x:v>
+      </x:c>
+      <x:c r="AA140"/>
+      <x:c r="AB140"/>
+      <x:c r="AC140"/>
+      <x:c r="AD140" t="str">
+        <x:v>수송선의 외관만 확인하고 돌아섰다.</x:v>
+      </x:c>
+      <x:c r="AE140" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF140" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG140" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH140" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI140" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ140" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="AK140" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL140"/>
+      <x:c r="AM140"/>
+      <x:c r="AN140"/>
+      <x:c r="AO140"/>
+      <x:c r="AP140"/>
+      <x:c r="AQ140"/>
+      <x:c r="AR140"/>
+      <x:c r="AS140"/>
+      <x:c r="AT140" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU140" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV140" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW140"/>
+      <x:c r="AX140"/>
+      <x:c r="AY140"/>
+      <x:c r="AZ140"/>
+      <x:c r="BA140"/>
+      <x:c r="BB140"/>
+      <x:c r="BC140"/>
+      <x:c r="BD140"/>
+      <x:c r="BE140" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF140" t="str">
+        <x:v>D1 Narrative v1.8: 비인물 소설식 상호작용. 수송선 기본 상태와 기술 잠금 선택 튜토리얼.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>FLOW_W1_SHIP_OVERVIEW</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>A01</x:v>
+      </x:c>
+      <x:c r="C141"/>
+      <x:c r="D141" t="str">
+        <x:v>OBJ_02_SHIP_CONSOLE</x:v>
+      </x:c>
+      <x:c r="E141" t="str">
+        <x:v>수송선의 현재 상태를 처음부터 확인한다</x:v>
+      </x:c>
+      <x:c r="F141"/>
+      <x:c r="G141"/>
+      <x:c r="H141" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="I141"/>
+      <x:c r="J141"/>
+      <x:c r="K141" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L141" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M141" t="str">
+        <x:v>함교, 엔진실, 연구구역, 거주구역.
+멀쩡한 곳은 없었지만 완전히 죽은 곳도 드물었다.
+고칠 수는 있다.
+문제는 무엇부터 고칠지다.
+수송선은 조용히 모래 위에 누워 있었다.</x:v>
+      </x:c>
+      <x:c r="N141" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O141"/>
+      <x:c r="P141"/>
+      <x:c r="Q141"/>
+      <x:c r="R141"/>
+      <x:c r="S141"/>
+      <x:c r="T141"/>
+      <x:c r="U141"/>
+      <x:c r="V141"/>
+      <x:c r="W141"/>
+      <x:c r="X141"/>
+      <x:c r="Y141"/>
+      <x:c r="Z141"/>
+      <x:c r="AA141"/>
+      <x:c r="AB141"/>
+      <x:c r="AC141"/>
+      <x:c r="AD141"/>
+      <x:c r="AE141" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF141" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG141" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH141" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI141" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ141" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="AK141" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL141"/>
+      <x:c r="AM141"/>
+      <x:c r="AN141"/>
+      <x:c r="AO141"/>
+      <x:c r="AP141"/>
+      <x:c r="AQ141"/>
+      <x:c r="AR141"/>
+      <x:c r="AS141"/>
+      <x:c r="AT141" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU141" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV141" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW141"/>
+      <x:c r="AX141"/>
+      <x:c r="AY141"/>
+      <x:c r="AZ141"/>
+      <x:c r="BA141"/>
+      <x:c r="BB141"/>
+      <x:c r="BC141"/>
+      <x:c r="BD141"/>
+      <x:c r="BE141" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF141" t="str">
+        <x:v>D1 Narrative v1.8: 비인물 소설식 상호작용. 수송선 기본 상태와 기술 잠금 선택 튜토리얼.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>FLOW_W1_SHIP_OVERVIEW</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>B01</x:v>
+      </x:c>
+      <x:c r="C142"/>
+      <x:c r="D142" t="str">
+        <x:v>OBJ_02_SHIP_CONSOLE</x:v>
+      </x:c>
+      <x:c r="E142" t="str">
+        <x:v>수송선의 현재 상태를 처음부터 확인한다</x:v>
+      </x:c>
+      <x:c r="F142"/>
+      <x:c r="G142"/>
+      <x:c r="H142" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="I142"/>
+      <x:c r="J142"/>
+      <x:c r="K142" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L142" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M142" t="str">
+        <x:v>제이는 비상 패널을 몇 번 두드려 손상 기록을 띄웠다.
+숫자는 좋지 않았다. 그래도 회로가 살아 있다는 건, 누군가 십 년 동안 이 배를 포기하지 않았다는 뜻이기도 했다.
+수송선은 조용히 모래 위에 누워 있었다.</x:v>
+      </x:c>
+      <x:c r="N142" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O142"/>
+      <x:c r="P142"/>
+      <x:c r="Q142"/>
+      <x:c r="R142"/>
+      <x:c r="S142"/>
+      <x:c r="T142"/>
+      <x:c r="U142"/>
+      <x:c r="V142"/>
+      <x:c r="W142"/>
+      <x:c r="X142"/>
+      <x:c r="Y142"/>
+      <x:c r="Z142"/>
+      <x:c r="AA142"/>
+      <x:c r="AB142"/>
+      <x:c r="AC142"/>
+      <x:c r="AD142"/>
+      <x:c r="AE142" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF142" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG142" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH142" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI142" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ142" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="AK142" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL142"/>
+      <x:c r="AM142"/>
+      <x:c r="AN142"/>
+      <x:c r="AO142"/>
+      <x:c r="AP142"/>
+      <x:c r="AQ142"/>
+      <x:c r="AR142"/>
+      <x:c r="AS142"/>
+      <x:c r="AT142" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU142" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV142" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW142"/>
+      <x:c r="AX142"/>
+      <x:c r="AY142"/>
+      <x:c r="AZ142"/>
+      <x:c r="BA142"/>
+      <x:c r="BB142"/>
+      <x:c r="BC142"/>
+      <x:c r="BD142"/>
+      <x:c r="BE142" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF142" t="str">
+        <x:v>D1 Narrative v1.8: 비인물 소설식 상호작용. 수송선 기본 상태와 기술 잠금 선택 튜토리얼.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>FLOW_W1_SHIP_OVERVIEW</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>C01</x:v>
+      </x:c>
+      <x:c r="C143"/>
+      <x:c r="D143" t="str">
+        <x:v>OBJ_02_SHIP_CONSOLE</x:v>
+      </x:c>
+      <x:c r="E143" t="str">
+        <x:v>수송선의 현재 상태를 처음부터 확인한다</x:v>
+      </x:c>
+      <x:c r="F143"/>
+      <x:c r="G143"/>
+      <x:c r="H143" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="I143"/>
+      <x:c r="J143"/>
+      <x:c r="K143" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L143" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M143" t="str">
+        <x:v>배를 오래 볼수록 해야 할 일이 늘어난다. 오늘은 여기까지만 보기로 한다.
+수송선은 조용히 모래 위에 누워 있었다.</x:v>
+      </x:c>
+      <x:c r="N143" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O143"/>
+      <x:c r="P143"/>
+      <x:c r="Q143"/>
+      <x:c r="R143"/>
+      <x:c r="S143"/>
+      <x:c r="T143"/>
+      <x:c r="U143"/>
+      <x:c r="V143"/>
+      <x:c r="W143"/>
+      <x:c r="X143"/>
+      <x:c r="Y143"/>
+      <x:c r="Z143"/>
+      <x:c r="AA143"/>
+      <x:c r="AB143"/>
+      <x:c r="AC143"/>
+      <x:c r="AD143"/>
+      <x:c r="AE143" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF143" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG143" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AH143" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI143" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ143" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="AK143" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL143"/>
+      <x:c r="AM143"/>
+      <x:c r="AN143"/>
+      <x:c r="AO143"/>
+      <x:c r="AP143"/>
+      <x:c r="AQ143"/>
+      <x:c r="AR143"/>
+      <x:c r="AS143"/>
+      <x:c r="AT143" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU143" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV143" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW143"/>
+      <x:c r="AX143"/>
+      <x:c r="AY143"/>
+      <x:c r="AZ143"/>
+      <x:c r="BA143"/>
+      <x:c r="BB143"/>
+      <x:c r="BC143"/>
+      <x:c r="BD143"/>
+      <x:c r="BE143" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF143" t="str">
+        <x:v>D1 Narrative v1.8: 비인물 소설식 상호작용. 수송선 기본 상태와 기술 잠금 선택 튜토리얼.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>A02</x:v>
+      </x:c>
+      <x:c r="C144"/>
+      <x:c r="D144" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E144" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F144" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G144" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H144" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I144"/>
+      <x:c r="J144"/>
+      <x:c r="K144" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="L144" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="M144" t="str">
+        <x:v>죽은 사람 얘기는 이런 게 낫더라. 어떻게 죽었는지보다, 어떻게 살았는지.</x:v>
+      </x:c>
+      <x:c r="N144" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O144" t="str">
+        <x:v>A03</x:v>
+      </x:c>
+      <x:c r="P144"/>
+      <x:c r="Q144"/>
+      <x:c r="R144"/>
+      <x:c r="S144"/>
+      <x:c r="T144"/>
+      <x:c r="U144"/>
+      <x:c r="V144"/>
+      <x:c r="W144"/>
+      <x:c r="X144"/>
+      <x:c r="Y144"/>
+      <x:c r="Z144"/>
+      <x:c r="AA144"/>
+      <x:c r="AB144"/>
+      <x:c r="AC144"/>
+      <x:c r="AD144"/>
+      <x:c r="AE144" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF144" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG144" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH144" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI144" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ144" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK144" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL144"/>
+      <x:c r="AM144"/>
+      <x:c r="AN144"/>
+      <x:c r="AO144"/>
+      <x:c r="AP144"/>
+      <x:c r="AQ144"/>
+      <x:c r="AR144"/>
+      <x:c r="AS144"/>
+      <x:c r="AT144" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU144" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV144" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW144"/>
+      <x:c r="AX144"/>
+      <x:c r="AY144"/>
+      <x:c r="AZ144"/>
+      <x:c r="BA144"/>
+      <x:c r="BB144"/>
+      <x:c r="BC144"/>
+      <x:c r="BD144"/>
+      <x:c r="BE144" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF144" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>A03</x:v>
+      </x:c>
+      <x:c r="C145"/>
+      <x:c r="D145" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E145" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F145" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G145" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H145" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I145"/>
+      <x:c r="J145"/>
+      <x:c r="K145" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L145" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M145" t="str">
+        <x:v>묘지는 그대로 남아 있었다.
+바람이 불 때마다 표식 사이의 천 조각들이 서로 다른 방향으로 흔들렸다.</x:v>
+      </x:c>
+      <x:c r="N145" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O145"/>
+      <x:c r="P145"/>
+      <x:c r="Q145"/>
+      <x:c r="R145"/>
+      <x:c r="S145"/>
+      <x:c r="T145"/>
+      <x:c r="U145"/>
+      <x:c r="V145"/>
+      <x:c r="W145"/>
+      <x:c r="X145"/>
+      <x:c r="Y145"/>
+      <x:c r="Z145"/>
+      <x:c r="AA145"/>
+      <x:c r="AB145"/>
+      <x:c r="AC145"/>
+      <x:c r="AD145"/>
+      <x:c r="AE145" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF145" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG145" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH145" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI145" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ145" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK145" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL145"/>
+      <x:c r="AM145"/>
+      <x:c r="AN145"/>
+      <x:c r="AO145"/>
+      <x:c r="AP145"/>
+      <x:c r="AQ145"/>
+      <x:c r="AR145"/>
+      <x:c r="AS145"/>
+      <x:c r="AT145" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU145" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV145" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW145"/>
+      <x:c r="AX145"/>
+      <x:c r="AY145"/>
+      <x:c r="AZ145"/>
+      <x:c r="BA145"/>
+      <x:c r="BB145"/>
+      <x:c r="BC145"/>
+      <x:c r="BD145"/>
+      <x:c r="BE145" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF145" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>B01</x:v>
+      </x:c>
+      <x:c r="C146"/>
+      <x:c r="D146" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E146" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F146" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G146" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H146" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I146"/>
+      <x:c r="J146"/>
+      <x:c r="K146" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="L146" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="M146" t="str">
+        <x:v>네가 오고 싶으면.</x:v>
+      </x:c>
+      <x:c r="N146" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O146" t="str">
+        <x:v>B02</x:v>
+      </x:c>
+      <x:c r="P146"/>
+      <x:c r="Q146"/>
+      <x:c r="R146"/>
+      <x:c r="S146"/>
+      <x:c r="T146"/>
+      <x:c r="U146"/>
+      <x:c r="V146"/>
+      <x:c r="W146"/>
+      <x:c r="X146"/>
+      <x:c r="Y146"/>
+      <x:c r="Z146"/>
+      <x:c r="AA146"/>
+      <x:c r="AB146"/>
+      <x:c r="AC146"/>
+      <x:c r="AD146"/>
+      <x:c r="AE146" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF146" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG146" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH146" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI146" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ146" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK146" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL146"/>
+      <x:c r="AM146"/>
+      <x:c r="AN146"/>
+      <x:c r="AO146"/>
+      <x:c r="AP146"/>
+      <x:c r="AQ146"/>
+      <x:c r="AR146"/>
+      <x:c r="AS146"/>
+      <x:c r="AT146" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU146" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV146" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW146"/>
+      <x:c r="AX146"/>
+      <x:c r="AY146"/>
+      <x:c r="AZ146"/>
+      <x:c r="BA146"/>
+      <x:c r="BB146"/>
+      <x:c r="BC146"/>
+      <x:c r="BD146"/>
+      <x:c r="BE146" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF146" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>B02</x:v>
+      </x:c>
+      <x:c r="C147"/>
+      <x:c r="D147" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E147" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F147" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G147" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H147" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I147"/>
+      <x:c r="J147"/>
+      <x:c r="K147" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L147" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M147" t="str">
+        <x:v>잠깐 뒤, 벤자민이 덧붙였다.</x:v>
+      </x:c>
+      <x:c r="N147" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O147" t="str">
+        <x:v>B03</x:v>
+      </x:c>
+      <x:c r="P147"/>
+      <x:c r="Q147"/>
+      <x:c r="R147"/>
+      <x:c r="S147"/>
+      <x:c r="T147"/>
+      <x:c r="U147"/>
+      <x:c r="V147"/>
+      <x:c r="W147"/>
+      <x:c r="X147"/>
+      <x:c r="Y147"/>
+      <x:c r="Z147"/>
+      <x:c r="AA147"/>
+      <x:c r="AB147"/>
+      <x:c r="AC147"/>
+      <x:c r="AD147"/>
+      <x:c r="AE147" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF147" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG147" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH147" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI147" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ147" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK147" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL147"/>
+      <x:c r="AM147"/>
+      <x:c r="AN147"/>
+      <x:c r="AO147"/>
+      <x:c r="AP147"/>
+      <x:c r="AQ147"/>
+      <x:c r="AR147"/>
+      <x:c r="AS147"/>
+      <x:c r="AT147" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU147" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV147" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW147"/>
+      <x:c r="AX147"/>
+      <x:c r="AY147"/>
+      <x:c r="AZ147"/>
+      <x:c r="BA147"/>
+      <x:c r="BB147"/>
+      <x:c r="BC147"/>
+      <x:c r="BD147"/>
+      <x:c r="BE147" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF147" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>B03</x:v>
+      </x:c>
+      <x:c r="C148"/>
+      <x:c r="D148" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E148" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F148" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G148" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H148" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I148"/>
+      <x:c r="J148"/>
+      <x:c r="K148" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="L148" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="M148" t="str">
+        <x:v>대신 불쌍한 표정은 하고 오지 마.</x:v>
+      </x:c>
+      <x:c r="N148" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O148" t="str">
+        <x:v>B04</x:v>
+      </x:c>
+      <x:c r="P148"/>
+      <x:c r="Q148"/>
+      <x:c r="R148"/>
+      <x:c r="S148"/>
+      <x:c r="T148"/>
+      <x:c r="U148"/>
+      <x:c r="V148"/>
+      <x:c r="W148"/>
+      <x:c r="X148"/>
+      <x:c r="Y148"/>
+      <x:c r="Z148"/>
+      <x:c r="AA148"/>
+      <x:c r="AB148"/>
+      <x:c r="AC148"/>
+      <x:c r="AD148"/>
+      <x:c r="AE148" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF148" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG148" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH148" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI148" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ148" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK148" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL148"/>
+      <x:c r="AM148"/>
+      <x:c r="AN148"/>
+      <x:c r="AO148"/>
+      <x:c r="AP148"/>
+      <x:c r="AQ148"/>
+      <x:c r="AR148"/>
+      <x:c r="AS148"/>
+      <x:c r="AT148" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU148" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV148" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW148"/>
+      <x:c r="AX148"/>
+      <x:c r="AY148"/>
+      <x:c r="AZ148"/>
+      <x:c r="BA148"/>
+      <x:c r="BB148"/>
+      <x:c r="BC148"/>
+      <x:c r="BD148"/>
+      <x:c r="BE148" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF148" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>B04</x:v>
+      </x:c>
+      <x:c r="C149"/>
+      <x:c r="D149" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E149" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F149" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G149" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H149" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I149"/>
+      <x:c r="J149"/>
+      <x:c r="K149" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L149" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M149" t="str">
+        <x:v>묘지는 그대로 남아 있었다.
+바람이 불 때마다 표식 사이의 천 조각들이 서로 다른 방향으로 흔들렸다.</x:v>
+      </x:c>
+      <x:c r="N149" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O149"/>
+      <x:c r="P149"/>
+      <x:c r="Q149"/>
+      <x:c r="R149"/>
+      <x:c r="S149"/>
+      <x:c r="T149"/>
+      <x:c r="U149"/>
+      <x:c r="V149"/>
+      <x:c r="W149"/>
+      <x:c r="X149"/>
+      <x:c r="Y149"/>
+      <x:c r="Z149"/>
+      <x:c r="AA149"/>
+      <x:c r="AB149"/>
+      <x:c r="AC149"/>
+      <x:c r="AD149"/>
+      <x:c r="AE149" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG149" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH149" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI149" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ149" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK149" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL149"/>
+      <x:c r="AM149"/>
+      <x:c r="AN149"/>
+      <x:c r="AO149"/>
+      <x:c r="AP149"/>
+      <x:c r="AQ149"/>
+      <x:c r="AR149"/>
+      <x:c r="AS149"/>
+      <x:c r="AT149" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV149" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW149"/>
+      <x:c r="AX149"/>
+      <x:c r="AY149"/>
+      <x:c r="AZ149"/>
+      <x:c r="BA149"/>
+      <x:c r="BB149"/>
+      <x:c r="BC149"/>
+      <x:c r="BD149"/>
+      <x:c r="BE149" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF149" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>FLOW_W1_BEN_NAMES</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>C01</x:v>
+      </x:c>
+      <x:c r="C150"/>
+      <x:c r="D150" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="E150" t="str">
+        <x:v>묘지에 같이 간다</x:v>
+      </x:c>
+      <x:c r="F150" t="str">
+        <x:v>QST_CHAR_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="G150" t="str">
+        <x:v>QSTEP_CHAR_BENJAMIN_01_NAMES</x:v>
+      </x:c>
+      <x:c r="H150" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I150"/>
+      <x:c r="J150"/>
+      <x:c r="K150" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L150" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M150" t="str">
+        <x:v>제이는 이름 두 개를 기억해 두고 묘지를 떠났다.
+바람이 불 때마다 표식 사이의 천 조각들이 서로 다른 방향으로 흔들렸다.</x:v>
+      </x:c>
+      <x:c r="N150" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O150"/>
+      <x:c r="P150"/>
+      <x:c r="Q150"/>
+      <x:c r="R150"/>
+      <x:c r="S150"/>
+      <x:c r="T150"/>
+      <x:c r="U150"/>
+      <x:c r="V150"/>
+      <x:c r="W150"/>
+      <x:c r="X150"/>
+      <x:c r="Y150"/>
+      <x:c r="Z150"/>
+      <x:c r="AA150"/>
+      <x:c r="AB150"/>
+      <x:c r="AC150"/>
+      <x:c r="AD150"/>
+      <x:c r="AE150" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG150" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="AH150" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI150" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ150" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="AK150" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL150"/>
+      <x:c r="AM150"/>
+      <x:c r="AN150"/>
+      <x:c r="AO150"/>
+      <x:c r="AP150"/>
+      <x:c r="AQ150"/>
+      <x:c r="AR150"/>
+      <x:c r="AS150"/>
+      <x:c r="AT150" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU150" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV150" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW150"/>
+      <x:c r="AX150"/>
+      <x:c r="AY150"/>
+      <x:c r="AZ150"/>
+      <x:c r="BA150"/>
+      <x:c r="BB150"/>
+      <x:c r="BC150"/>
+      <x:c r="BD150"/>
+      <x:c r="BE150" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF150" t="str">
+        <x:v>Narrative UX v1.9: 정보 하나 → 입력 → 반응 → 다음 정보 Beat. 대사/내레이션 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>FLOW_W1_REUNION_DIYA</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>N02</x:v>
+      </x:c>
+      <x:c r="C153"/>
+      <x:c r="D153" t="str">
+        <x:v>CHA_DIYA</x:v>
+      </x:c>
+      <x:c r="E153" t="str">
+        <x:v>거주지의 변화를 묻는다</x:v>
+      </x:c>
+      <x:c r="F153" t="str">
+        <x:v>QST_W1_MAIN_01_AWAKE</x:v>
+      </x:c>
+      <x:c r="G153" t="str">
+        <x:v>QSTEP_W1_MAIN_01_AWAKE_01</x:v>
+      </x:c>
+      <x:c r="H153" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I153"/>
+      <x:c r="J153"/>
+      <x:c r="K153" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L153" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M153" t="str">
+        <x:v>덧댄 벽, 말린 옷, 아이가 그린 표식이 차례로 눈에 들어온다.
+임시로 세운 것들에는 십 년 동안 고친 흔적이 겹겹이 남아 있었다.</x:v>
+      </x:c>
+      <x:c r="N153" t="str">
+        <x:v>여긴 정말 달라졌네?</x:v>
+      </x:c>
+      <x:c r="O153" t="str">
+        <x:v>N03</x:v>
+      </x:c>
+      <x:c r="P153"/>
+      <x:c r="Q153"/>
+      <x:c r="R153"/>
+      <x:c r="S153"/>
+      <x:c r="T153"/>
+      <x:c r="U153"/>
+      <x:c r="V153"/>
+      <x:c r="W153"/>
+      <x:c r="X153"/>
+      <x:c r="Y153"/>
+      <x:c r="Z153"/>
+      <x:c r="AA153"/>
+      <x:c r="AB153"/>
+      <x:c r="AC153"/>
+      <x:c r="AD153"/>
+      <x:c r="AE153" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF153" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG153" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH153" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI153" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ153" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="AK153" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL153"/>
+      <x:c r="AM153"/>
+      <x:c r="AN153"/>
+      <x:c r="AO153"/>
+      <x:c r="AP153"/>
+      <x:c r="AQ153"/>
+      <x:c r="AR153"/>
+      <x:c r="AS153"/>
+      <x:c r="AT153" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU153" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV153" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW153"/>
+      <x:c r="AX153"/>
+      <x:c r="AY153"/>
+      <x:c r="AZ153"/>
+      <x:c r="BA153"/>
+      <x:c r="BB153"/>
+      <x:c r="BC153"/>
+      <x:c r="BD153"/>
+      <x:c r="BE153" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF153" t="str">
+        <x:v>Narrative UX v1.9: 행동 선택에 시간비용 부여. 내레이션과 대사 Beat 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>FLOW_W1_REUNION_DIYA</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>N03</x:v>
+      </x:c>
+      <x:c r="C154"/>
+      <x:c r="D154" t="str">
+        <x:v>CHA_DIYA</x:v>
+      </x:c>
+      <x:c r="E154" t="str">
+        <x:v>거주지의 변화를 묻는다</x:v>
+      </x:c>
+      <x:c r="F154" t="str">
+        <x:v>QST_W1_MAIN_01_AWAKE</x:v>
+      </x:c>
+      <x:c r="G154" t="str">
+        <x:v>QSTEP_W1_MAIN_01_AWAKE_01</x:v>
+      </x:c>
+      <x:c r="H154" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I154"/>
+      <x:c r="J154"/>
+      <x:c r="K154" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="L154" t="str">
+        <x:v>CHA_DIYA</x:v>
+      </x:c>
+      <x:c r="M154" t="str">
+        <x:v>네가 잠든 사이 임시라는 말이 조금씩 거짓말이 됐어.</x:v>
+      </x:c>
+      <x:c r="N154" t="str">
+        <x:v>그 말을 기억해 둔다.</x:v>
+      </x:c>
+      <x:c r="O154" t="str">
+        <x:v>N04</x:v>
+      </x:c>
+      <x:c r="P154"/>
+      <x:c r="Q154"/>
+      <x:c r="R154"/>
+      <x:c r="S154"/>
+      <x:c r="T154"/>
+      <x:c r="U154"/>
+      <x:c r="V154"/>
+      <x:c r="W154"/>
+      <x:c r="X154"/>
+      <x:c r="Y154"/>
+      <x:c r="Z154"/>
+      <x:c r="AA154"/>
+      <x:c r="AB154"/>
+      <x:c r="AC154"/>
+      <x:c r="AD154"/>
+      <x:c r="AE154" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF154" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG154" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH154" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI154" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ154" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="AK154" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL154"/>
+      <x:c r="AM154"/>
+      <x:c r="AN154"/>
+      <x:c r="AO154"/>
+      <x:c r="AP154"/>
+      <x:c r="AQ154"/>
+      <x:c r="AR154"/>
+      <x:c r="AS154"/>
+      <x:c r="AT154" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU154" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV154" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW154"/>
+      <x:c r="AX154"/>
+      <x:c r="AY154"/>
+      <x:c r="AZ154"/>
+      <x:c r="BA154"/>
+      <x:c r="BB154"/>
+      <x:c r="BC154"/>
+      <x:c r="BD154"/>
+      <x:c r="BE154" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF154" t="str">
+        <x:v>Narrative UX v1.9: 행동 선택에 시간비용 부여. 내레이션과 대사 Beat 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>FLOW_W1_REUNION_DIYA</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>N04</x:v>
+      </x:c>
+      <x:c r="C155"/>
+      <x:c r="D155" t="str">
+        <x:v>CHA_DIYA</x:v>
+      </x:c>
+      <x:c r="E155" t="str">
+        <x:v>거주지의 변화를 묻는다</x:v>
+      </x:c>
+      <x:c r="F155" t="str">
+        <x:v>QST_W1_MAIN_01_AWAKE</x:v>
+      </x:c>
+      <x:c r="G155" t="str">
+        <x:v>QSTEP_W1_MAIN_01_AWAKE_01</x:v>
+      </x:c>
+      <x:c r="H155" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I155"/>
+      <x:c r="J155"/>
+      <x:c r="K155" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="L155" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="M155" t="str">
+        <x:v>한 바퀴를 돌아 출발점에 도착했을 때, 처음 보았던 텐트 자리가 전보다 조금 다르게 보였다.</x:v>
+      </x:c>
+      <x:c r="N155" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O155"/>
+      <x:c r="P155"/>
+      <x:c r="Q155"/>
+      <x:c r="R155"/>
+      <x:c r="S155"/>
+      <x:c r="T155"/>
+      <x:c r="U155"/>
+      <x:c r="V155"/>
+      <x:c r="W155"/>
+      <x:c r="X155"/>
+      <x:c r="Y155"/>
+      <x:c r="Z155"/>
+      <x:c r="AA155"/>
+      <x:c r="AB155"/>
+      <x:c r="AC155"/>
+      <x:c r="AD155"/>
+      <x:c r="AE155" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF155" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG155" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH155" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI155" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ155" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="AK155" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL155"/>
+      <x:c r="AM155"/>
+      <x:c r="AN155"/>
+      <x:c r="AO155"/>
+      <x:c r="AP155"/>
+      <x:c r="AQ155"/>
+      <x:c r="AR155"/>
+      <x:c r="AS155"/>
+      <x:c r="AT155" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU155" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV155" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW155"/>
+      <x:c r="AX155"/>
+      <x:c r="AY155"/>
+      <x:c r="AZ155"/>
+      <x:c r="BA155"/>
+      <x:c r="BB155"/>
+      <x:c r="BC155"/>
+      <x:c r="BD155"/>
+      <x:c r="BE155" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF155" t="str">
+        <x:v>Narrative UX v1.9: 행동 선택에 시간비용 부여. 내레이션과 대사 Beat 분리.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>FLOW_W1_REUNION_BORICHI</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>N02</x:v>
+      </x:c>
+      <x:c r="C156"/>
+      <x:c r="D156" t="str">
+        <x:v>CHA_BORICHI</x:v>
+      </x:c>
+      <x:c r="E156" t="str">
+        <x:v>보리치에게 이 행성의 날씨를 묻는다</x:v>
+      </x:c>
+      <x:c r="F156" t="str">
+        <x:v>QST_W1_MAIN_01_AWAKE</x:v>
+      </x:c>
+      <x:c r="G156" t="str">
+        <x:v>QSTEP_W1_MAIN_01_AWAKE_01</x:v>
+      </x:c>
+      <x:c r="H156" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I156"/>
+      <x:c r="J156"/>
+      <x:c r="K156" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="L156" t="str">
+        <x:v>CHA_BORICHI</x:v>
+      </x:c>
+      <x:c r="M156" t="str">
+        <x:v>오늘 바람이 조금 틀어졌어. 큰 차이는 아닌데…</x:v>
+      </x:c>
+      <x:c r="N156" t="str">
+        <x:v>기록을 전부 보고 있었구나.</x:v>
+      </x:c>
+      <x:c r="O156" t="str">
+        <x:v>N03</x:v>
+      </x:c>
+      <x:c r="P156"/>
+      <x:c r="Q156"/>
+      <x:c r="R156"/>
+      <x:c r="S156"/>
+      <x:c r="T156"/>
+      <x:c r="U156"/>
+      <x:c r="V156"/>
+      <x:c r="W156"/>
+      <x:c r="X156"/>
+      <x:c r="Y156"/>
+      <x:c r="Z156"/>
+      <x:c r="AA156"/>
+      <x:c r="AB156"/>
+      <x:c r="AC156"/>
+      <x:c r="AD156"/>
+      <x:c r="AE156" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF156" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG156" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH156" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI156" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ156" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="AK156" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL156"/>
+      <x:c r="AM156"/>
+      <x:c r="AN156"/>
+      <x:c r="AO156"/>
+      <x:c r="AP156"/>
+      <x:c r="AQ156"/>
+      <x:c r="AR156"/>
+      <x:c r="AS156"/>
+      <x:c r="AT156" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU156" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV156" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW156"/>
+      <x:c r="AX156"/>
+      <x:c r="AY156"/>
+      <x:c r="AZ156"/>
+      <x:c r="BA156"/>
+      <x:c r="BB156"/>
+      <x:c r="BC156"/>
+      <x:c r="BD156"/>
+      <x:c r="BE156" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF156" t="str">
+        <x:v>Narrative UX v1.9: 내레이션과 인물 대사를 같은 BodyText에 섞지 않음.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>FLOW_W1_REUNION_BORICHI</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>N03</x:v>
+      </x:c>
+      <x:c r="C157"/>
+      <x:c r="D157" t="str">
+        <x:v>CHA_BORICHI</x:v>
+      </x:c>
+      <x:c r="E157" t="str">
+        <x:v>보리치에게 이 행성의 날씨를 묻는다</x:v>
+      </x:c>
+      <x:c r="F157" t="str">
+        <x:v>QST_W1_MAIN_01_AWAKE</x:v>
+      </x:c>
+      <x:c r="G157" t="str">
+        <x:v>QSTEP_W1_MAIN_01_AWAKE_01</x:v>
+      </x:c>
+      <x:c r="H157" t="str">
+        <x:v>PROGRESS</x:v>
+      </x:c>
+      <x:c r="I157"/>
+      <x:c r="J157"/>
+      <x:c r="K157" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="L157" t="str">
+        <x:v>CHA_BORICHI</x:v>
+      </x:c>
+      <x:c r="M157" t="str">
+        <x:v>작은 차이를 놓치면 사람이 죽으니까.</x:v>
+      </x:c>
+      <x:c r="N157" t="str">
+        <x:v>계속</x:v>
+      </x:c>
+      <x:c r="O157"/>
+      <x:c r="P157"/>
+      <x:c r="Q157"/>
+      <x:c r="R157"/>
+      <x:c r="S157"/>
+      <x:c r="T157"/>
+      <x:c r="U157"/>
+      <x:c r="V157"/>
+      <x:c r="W157"/>
+      <x:c r="X157"/>
+      <x:c r="Y157"/>
+      <x:c r="Z157"/>
+      <x:c r="AA157"/>
+      <x:c r="AB157"/>
+      <x:c r="AC157"/>
+      <x:c r="AD157"/>
+      <x:c r="AE157" t="str">
+        <x:v>MENU_OPTION</x:v>
+      </x:c>
+      <x:c r="AF157" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG157" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AH157" t="str">
+        <x:v>MORNING|AFTERNOON|EVENING</x:v>
+      </x:c>
+      <x:c r="AI157" t="str">
+        <x:v>ONCE</x:v>
+      </x:c>
+      <x:c r="AJ157" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="AK157" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AL157"/>
+      <x:c r="AM157"/>
+      <x:c r="AN157"/>
+      <x:c r="AO157"/>
+      <x:c r="AP157"/>
+      <x:c r="AQ157"/>
+      <x:c r="AR157"/>
+      <x:c r="AS157"/>
+      <x:c r="AT157" t="str">
+        <x:v>NONE</x:v>
+      </x:c>
+      <x:c r="AU157" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AV157" t="str">
+        <x:v>AND</x:v>
+      </x:c>
+      <x:c r="AW157"/>
+      <x:c r="AX157"/>
+      <x:c r="AY157"/>
+      <x:c r="AZ157"/>
+      <x:c r="BA157"/>
+      <x:c r="BB157"/>
+      <x:c r="BC157"/>
+      <x:c r="BD157"/>
+      <x:c r="BE157" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="BF157" t="str">
+        <x:v>Narrative UX v1.9: 내레이션과 인물 대사를 같은 BodyText에 섞지 않음.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -40351,20 +42851,44 @@
       </x:c>
     </x:row>
     <x:row r="52" ht="38.099998474121094" customHeight="1">
-      <x:c r="A52" s="20"/>
-      <x:c r="B52" s="21"/>
-      <x:c r="C52" s="21"/>
-      <x:c r="D52" s="21"/>
-      <x:c r="E52" s="21"/>
-      <x:c r="F52" s="28"/>
+      <x:c r="A52" s="20" t="str">
+        <x:v>STA_W1_SHIP_OVERVIEW_SEEN</x:v>
+      </x:c>
+      <x:c r="B52" s="21" t="str">
+        <x:v>BOOL</x:v>
+      </x:c>
+      <x:c r="C52" s="21" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="D52" s="21" t="str">
+        <x:v>INFO</x:v>
+      </x:c>
+      <x:c r="E52" s="21" t="str">
+        <x:v>수송선의 기본 상태를 직접 확인함</x:v>
+      </x:c>
+      <x:c r="F52" s="28" t="str">
+        <x:v>D1 Narrative v1.8 수송선 첫 점검.</x:v>
+      </x:c>
     </x:row>
     <x:row r="53" ht="38.099998474121094" customHeight="1">
-      <x:c r="A53" s="20"/>
-      <x:c r="B53" s="21"/>
-      <x:c r="C53" s="21"/>
-      <x:c r="D53" s="21"/>
-      <x:c r="E53" s="21"/>
-      <x:c r="F53" s="28"/>
+      <x:c r="A53" s="20" t="str">
+        <x:v>STA_W1_SHIP_DETAIL_SEEN</x:v>
+      </x:c>
+      <x:c r="B53" s="21" t="str">
+        <x:v>BOOL</x:v>
+      </x:c>
+      <x:c r="C53" s="21" t="str">
+        <x:v>FALSE</x:v>
+      </x:c>
+      <x:c r="D53" s="21" t="str">
+        <x:v>INFO</x:v>
+      </x:c>
+      <x:c r="E53" s="21" t="str">
+        <x:v>수송선 손상 기록까지 확인함</x:v>
+      </x:c>
+      <x:c r="F53" s="28" t="str">
+        <x:v>D1 Narrative v1.8 기술 선택 결과.</x:v>
+      </x:c>
     </x:row>
     <x:row r="54" ht="38.099998474121094" customHeight="1">
       <x:c r="A54" s="20"/>
@@ -47501,7 +50025,7 @@
         <x:v>가장 친했던 동료의 변화에서 시간 공백을 체감한다.</x:v>
       </x:c>
       <x:c r="F86" s="21" t="str">
-        <x:v>벤자민이 제이의 상태를 확인하며 깨어난 것을 반긴다.</x:v>
+        <x:v>벤자민이 제이의 상태를 확인하고, 제이는 자신이 10년을 건너뛰었다는 사실을 처음 받아들인다.</x:v>
       </x:c>
       <x:c r="G86" s="21" t="str">
         <x:v>NARRATIVE</x:v>
@@ -47513,19 +50037,29 @@
         <x:v>CHA_BENJAMIN</x:v>
       </x:c>
       <x:c r="J86" s="21" t="str">
-        <x:v>“제이. 들려?” 벤자민은 웃으려다가 그만둔다. “좋아. 눈은 제대로 뜨네. 천천히 일어나. 네가 생각하는 것보다 시간이 많이 지났어.”</x:v>
+        <x:v>눈 떠. 천천히.</x:v>
       </x:c>
       <x:c r="K86" s="21" t="str">
-        <x:v>얼마나 지났는데?</x:v>
+        <x:v>…벤자민?</x:v>
       </x:c>
       <x:c r="L86" s="21" t="str">
         <x:v>N03</x:v>
       </x:c>
-      <x:c r="M86" s="21"/>
-      <x:c r="N86" s="21"/>
-      <x:c r="O86" s="21"/>
-      <x:c r="P86" s="21"/>
-      <x:c r="Q86" s="21"/>
+      <x:c r="M86" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N86" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O86" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P86" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q86" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="R86" s="21"/>
       <x:c r="S86" s="21"/>
       <x:c r="T86" s="21"/>
@@ -47558,7 +50092,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AU86" t="str">
-        <x:v>벤자민이 제이를 직접 깨우는 오프닝.</x:v>
+        <x:v>D1 Narrative v1.8: 짧은 턴이 아래로 이어지는 오프닝. 설정을 한 번에 설명하지 않음.</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="38.099998474121094" customHeight="1">
@@ -47573,10 +50107,10 @@
         <x:v>다시 눈을 뜨다</x:v>
       </x:c>
       <x:c r="E87" s="21" t="str">
-        <x:v>출항 목표보다 ‘현재 상황 파악’을 플레이어의 첫 목표로 둔다.</x:v>
+        <x:v>가장 친했던 동료의 변화에서 시간 공백을 체감한다.</x:v>
       </x:c>
       <x:c r="F87" s="21" t="str">
-        <x:v>사고와 생존자들에 대한 최소 정보만 듣는다.</x:v>
+        <x:v>벤자민이 제이의 상태를 확인하고, 제이는 자신이 10년을 건너뛰었다는 사실을 처음 받아들인다.</x:v>
       </x:c>
       <x:c r="G87" s="21" t="str">
         <x:v>NARRATIVE</x:v>
@@ -47585,22 +50119,32 @@
         <x:v>DIALOGUE</x:v>
       </x:c>
       <x:c r="I87" s="21" t="str">
-        <x:v>PLAYER</x:v>
+        <x:v>CHA_BENJAMIN</x:v>
       </x:c>
       <x:c r="J87" s="21" t="str">
-        <x:v>기억은 이어져 있다. 지구를 떠났고, 다른 행성으로 향했고, 그리고 착륙 직전까지. 그 다음이 비어 있다.</x:v>
+        <x:v>그래. 기억은 멀쩡하네.</x:v>
       </x:c>
       <x:c r="K87" s="21" t="str">
-        <x:v>사고 뒤엔 무슨 일이 있었어?</x:v>
+        <x:v>도착한 거야?</x:v>
       </x:c>
       <x:c r="L87" s="21" t="str">
         <x:v>N04</x:v>
       </x:c>
-      <x:c r="M87" s="21"/>
-      <x:c r="N87" s="21"/>
-      <x:c r="O87" s="21"/>
-      <x:c r="P87" s="21"/>
-      <x:c r="Q87" s="21"/>
+      <x:c r="M87" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N87" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O87" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P87" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q87" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="R87" s="21"/>
       <x:c r="S87" s="21"/>
       <x:c r="T87" s="21"/>
@@ -47632,7 +50176,9 @@
       <x:c r="AT87" s="268" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AU87"/>
+      <x:c r="AU87" t="str">
+        <x:v>D1 Narrative v1.8: 짧은 턴이 아래로 이어지는 오프닝. 설정을 한 번에 설명하지 않음.</x:v>
+      </x:c>
     </x:row>
     <x:row r="88" ht="38.099998474121094" customHeight="1">
       <x:c r="A88" s="20" t="str">
@@ -47646,50 +50192,54 @@
         <x:v>다시 눈을 뜨다</x:v>
       </x:c>
       <x:c r="E88" s="21" t="str">
-        <x:v>플레이어를 허브로 내보내고 핵심 동료 6명 재회 Main을 시작한다.</x:v>
+        <x:v>가장 친했던 동료의 변화에서 시간 공백을 체감한다.</x:v>
       </x:c>
       <x:c r="F88" s="21" t="str">
-        <x:v>벤자민과 재회가 체크되고, 다른 동료들을 직접 만나야 한다는 현재 목표가 생긴다.</x:v>
+        <x:v>벤자민이 제이의 상태를 확인하고, 제이는 자신이 10년을 건너뛰었다는 사실을 처음 받아들인다.</x:v>
       </x:c>
       <x:c r="G88" s="21" t="str">
         <x:v>NARRATIVE</x:v>
       </x:c>
       <x:c r="H88" s="21" t="str">
-        <x:v>DIALOGUE</x:v>
+        <x:v>NARRATION</x:v>
       </x:c>
       <x:c r="I88" s="21" t="str">
-        <x:v>CHA_BENJAMIN</x:v>
+        <x:v>NARRATOR</x:v>
       </x:c>
       <x:c r="J88" s="21" t="str">
-        <x:v>“우린 불시착했고, 살아남은 사람들은 여기서 버텼어. 네가 기억하는 그대로인 사람은 별로 없을 거야.” 벤자민은 잠깐 말을 멈춘다. “샘부터 만나. 아니, 그냥 다 만나봐. 네가 직접 보는 게 나아.”</x:v>
+        <x:v>벤자민은 대답하지 않고 냉동 캡슐의 잠금 장치를 끝까지 풀었다.</x:v>
       </x:c>
       <x:c r="K88" s="21" t="str">
-        <x:v>밖으로 나간다.</x:v>
-      </x:c>
-      <x:c r="L88" s="21"/>
-      <x:c r="M88" s="21"/>
-      <x:c r="N88" s="21"/>
-      <x:c r="O88" s="21"/>
-      <x:c r="P88" s="21"/>
-      <x:c r="Q88" s="21"/>
+        <x:v>계속 듣는다.</x:v>
+      </x:c>
+      <x:c r="L88" s="21" t="str">
+        <x:v>N05</x:v>
+      </x:c>
+      <x:c r="M88" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N88" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O88" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P88" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q88" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="R88" s="21"/>
       <x:c r="S88" s="21"/>
       <x:c r="T88" s="21"/>
       <x:c r="U88" s="21"/>
       <x:c r="V88" s="21"/>
       <x:c r="W88" s="21"/>
-      <x:c r="X88" s="28" t="str">
-        <x:v>STA_W1_MET_BENJAMIN</x:v>
-      </x:c>
-      <x:c r="Y88" t="str">
-        <x:v>SET TRUE</x:v>
-      </x:c>
-      <x:c r="Z88" t="str">
-        <x:v>STA_W1_REUNION_COUNT</x:v>
-      </x:c>
-      <x:c r="AA88" t="str">
-        <x:v>ADD 1</x:v>
-      </x:c>
+      <x:c r="X88" s="28"/>
+      <x:c r="Y88"/>
+      <x:c r="Z88"/>
+      <x:c r="AA88"/>
       <x:c r="AB88"/>
       <x:c r="AC88"/>
       <x:c r="AD88"/>
@@ -47712,27 +50262,59 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AU88" t="str">
-        <x:v>도입 Main 체크리스트의 벤자민 항목을 시작부터 완료.</x:v>
+        <x:v>D1 Narrative v1.8: 짧은 턴이 아래로 이어지는 오프닝. 설정을 한 번에 설명하지 않음.</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="38.099998474121094" customHeight="1">
-      <x:c r="A89" s="20"/>
-      <x:c r="B89" s="21"/>
+      <x:c r="A89" s="20" t="str">
+        <x:v>EVT_W1_GAME_START</x:v>
+      </x:c>
+      <x:c r="B89" s="21" t="str">
+        <x:v>N05</x:v>
+      </x:c>
       <x:c r="C89" s="21"/>
-      <x:c r="D89" s="21"/>
-      <x:c r="E89" s="21"/>
-      <x:c r="F89" s="21"/>
-      <x:c r="G89" s="21"/>
-      <x:c r="H89" s="21"/>
-      <x:c r="I89" s="21"/>
-      <x:c r="J89" s="21"/>
-      <x:c r="K89" s="21"/>
-      <x:c r="L89" s="21"/>
-      <x:c r="M89" s="21"/>
-      <x:c r="N89" s="21"/>
-      <x:c r="O89" s="21"/>
-      <x:c r="P89" s="21"/>
-      <x:c r="Q89" s="21"/>
+      <x:c r="D89" s="21" t="str">
+        <x:v>다시 눈을 뜨다</x:v>
+      </x:c>
+      <x:c r="E89" s="21" t="str">
+        <x:v>가장 친했던 동료의 변화에서 시간 공백을 체감한다.</x:v>
+      </x:c>
+      <x:c r="F89" s="21" t="str">
+        <x:v>벤자민이 제이의 상태를 확인하고, 제이는 자신이 10년을 건너뛰었다는 사실을 처음 받아들인다.</x:v>
+      </x:c>
+      <x:c r="G89" s="21" t="str">
+        <x:v>NARRATIVE</x:v>
+      </x:c>
+      <x:c r="H89" s="21" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="I89" s="21" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="J89" s="21" t="str">
+        <x:v>도착은 했지. 예정대로는 아니고.</x:v>
+      </x:c>
+      <x:c r="K89" s="21" t="str">
+        <x:v>무슨 일이 있었어?</x:v>
+      </x:c>
+      <x:c r="L89" s="21" t="str">
+        <x:v>N06</x:v>
+      </x:c>
+      <x:c r="M89" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N89" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O89" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P89" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q89" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="R89" s="21"/>
       <x:c r="S89" s="21"/>
       <x:c r="T89" s="21"/>
@@ -47740,25 +50322,84 @@
       <x:c r="V89" s="21"/>
       <x:c r="W89" s="21"/>
       <x:c r="X89" s="28"/>
+      <x:c r="Y89"/>
+      <x:c r="Z89"/>
+      <x:c r="AA89"/>
+      <x:c r="AB89"/>
+      <x:c r="AC89"/>
+      <x:c r="AD89"/>
+      <x:c r="AE89"/>
+      <x:c r="AF89"/>
+      <x:c r="AG89"/>
+      <x:c r="AH89"/>
+      <x:c r="AI89"/>
+      <x:c r="AJ89"/>
+      <x:c r="AK89"/>
+      <x:c r="AL89"/>
+      <x:c r="AM89"/>
+      <x:c r="AN89"/>
+      <x:c r="AO89"/>
+      <x:c r="AP89"/>
+      <x:c r="AQ89"/>
+      <x:c r="AR89"/>
+      <x:c r="AS89"/>
+      <x:c r="AT89" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU89" t="str">
+        <x:v>D1 Narrative v1.8: 짧은 턴이 아래로 이어지는 오프닝. 설정을 한 번에 설명하지 않음.</x:v>
+      </x:c>
     </x:row>
     <x:row r="90" ht="38.099998474121094" customHeight="1">
-      <x:c r="A90" s="20"/>
-      <x:c r="B90" s="21"/>
+      <x:c r="A90" s="20" t="str">
+        <x:v>EVT_W1_GAME_START</x:v>
+      </x:c>
+      <x:c r="B90" s="21" t="str">
+        <x:v>N06</x:v>
+      </x:c>
       <x:c r="C90" s="21"/>
-      <x:c r="D90" s="21"/>
-      <x:c r="E90" s="21"/>
-      <x:c r="F90" s="21"/>
-      <x:c r="G90" s="21"/>
-      <x:c r="H90" s="21"/>
-      <x:c r="I90" s="21"/>
-      <x:c r="J90" s="21"/>
-      <x:c r="K90" s="21"/>
-      <x:c r="L90" s="21"/>
-      <x:c r="M90" s="21"/>
-      <x:c r="N90" s="21"/>
-      <x:c r="O90" s="21"/>
-      <x:c r="P90" s="21"/>
-      <x:c r="Q90" s="21"/>
+      <x:c r="D90" s="21" t="str">
+        <x:v>다시 눈을 뜨다</x:v>
+      </x:c>
+      <x:c r="E90" s="21" t="str">
+        <x:v>가장 친했던 동료의 변화에서 시간 공백을 체감한다.</x:v>
+      </x:c>
+      <x:c r="F90" s="21" t="str">
+        <x:v>벤자민이 제이의 상태를 확인하고, 제이는 자신이 10년을 건너뛰었다는 사실을 처음 받아들인다.</x:v>
+      </x:c>
+      <x:c r="G90" s="21" t="str">
+        <x:v>NARRATIVE</x:v>
+      </x:c>
+      <x:c r="H90" s="21" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="I90" s="21" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="J90" s="21" t="str">
+        <x:v>착륙 사고. 열 해 전.</x:v>
+      </x:c>
+      <x:c r="K90" s="21" t="str">
+        <x:v>…열 해?</x:v>
+      </x:c>
+      <x:c r="L90" s="21" t="str">
+        <x:v>N07</x:v>
+      </x:c>
+      <x:c r="M90" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N90" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O90" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P90" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q90" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="R90" s="21"/>
       <x:c r="S90" s="21"/>
       <x:c r="T90" s="21"/>
@@ -47766,25 +50407,84 @@
       <x:c r="V90" s="21"/>
       <x:c r="W90" s="21"/>
       <x:c r="X90" s="28"/>
+      <x:c r="Y90"/>
+      <x:c r="Z90"/>
+      <x:c r="AA90"/>
+      <x:c r="AB90"/>
+      <x:c r="AC90"/>
+      <x:c r="AD90"/>
+      <x:c r="AE90"/>
+      <x:c r="AF90"/>
+      <x:c r="AG90"/>
+      <x:c r="AH90"/>
+      <x:c r="AI90"/>
+      <x:c r="AJ90"/>
+      <x:c r="AK90"/>
+      <x:c r="AL90"/>
+      <x:c r="AM90"/>
+      <x:c r="AN90"/>
+      <x:c r="AO90"/>
+      <x:c r="AP90"/>
+      <x:c r="AQ90"/>
+      <x:c r="AR90"/>
+      <x:c r="AS90"/>
+      <x:c r="AT90" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU90" t="str">
+        <x:v>D1 Narrative v1.8: 짧은 턴이 아래로 이어지는 오프닝. 설정을 한 번에 설명하지 않음.</x:v>
+      </x:c>
     </x:row>
     <x:row r="91" ht="38.099998474121094" customHeight="1">
-      <x:c r="A91" s="20"/>
-      <x:c r="B91" s="21"/>
+      <x:c r="A91" s="20" t="str">
+        <x:v>EVT_W1_GAME_START</x:v>
+      </x:c>
+      <x:c r="B91" s="21" t="str">
+        <x:v>N07</x:v>
+      </x:c>
       <x:c r="C91" s="21"/>
-      <x:c r="D91" s="21"/>
-      <x:c r="E91" s="21"/>
-      <x:c r="F91" s="21"/>
-      <x:c r="G91" s="21"/>
-      <x:c r="H91" s="21"/>
-      <x:c r="I91" s="21"/>
-      <x:c r="J91" s="21"/>
-      <x:c r="K91" s="21"/>
-      <x:c r="L91" s="21"/>
-      <x:c r="M91" s="21"/>
-      <x:c r="N91" s="21"/>
-      <x:c r="O91" s="21"/>
-      <x:c r="P91" s="21"/>
-      <x:c r="Q91" s="21"/>
+      <x:c r="D91" s="21" t="str">
+        <x:v>다시 눈을 뜨다</x:v>
+      </x:c>
+      <x:c r="E91" s="21" t="str">
+        <x:v>가장 친했던 동료의 변화에서 시간 공백을 체감한다.</x:v>
+      </x:c>
+      <x:c r="F91" s="21" t="str">
+        <x:v>벤자민이 제이의 상태를 확인하고, 제이는 자신이 10년을 건너뛰었다는 사실을 처음 받아들인다.</x:v>
+      </x:c>
+      <x:c r="G91" s="21" t="str">
+        <x:v>NARRATIVE</x:v>
+      </x:c>
+      <x:c r="H91" s="21" t="str">
+        <x:v>DIALOGUE</x:v>
+      </x:c>
+      <x:c r="I91" s="21" t="str">
+        <x:v>CHA_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="J91" s="21" t="str">
+        <x:v>넌 그동안 잤고, 우린 여기서 살았어.</x:v>
+      </x:c>
+      <x:c r="K91" s="21" t="str">
+        <x:v>사람부터 만나볼게.</x:v>
+      </x:c>
+      <x:c r="L91" s="21" t="str">
+        <x:v>N08</x:v>
+      </x:c>
+      <x:c r="M91" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N91" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O91" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P91" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q91" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="R91" s="21"/>
       <x:c r="S91" s="21"/>
       <x:c r="T91" s="21"/>
@@ -47792,32 +50492,128 @@
       <x:c r="V91" s="21"/>
       <x:c r="W91" s="21"/>
       <x:c r="X91" s="28"/>
+      <x:c r="Y91"/>
+      <x:c r="Z91"/>
+      <x:c r="AA91"/>
+      <x:c r="AB91"/>
+      <x:c r="AC91"/>
+      <x:c r="AD91"/>
+      <x:c r="AE91"/>
+      <x:c r="AF91"/>
+      <x:c r="AG91"/>
+      <x:c r="AH91"/>
+      <x:c r="AI91"/>
+      <x:c r="AJ91"/>
+      <x:c r="AK91"/>
+      <x:c r="AL91"/>
+      <x:c r="AM91"/>
+      <x:c r="AN91"/>
+      <x:c r="AO91"/>
+      <x:c r="AP91"/>
+      <x:c r="AQ91"/>
+      <x:c r="AR91"/>
+      <x:c r="AS91"/>
+      <x:c r="AT91" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU91" t="str">
+        <x:v>D1 Narrative v1.8: 짧은 턴이 아래로 이어지는 오프닝. 설정을 한 번에 설명하지 않음.</x:v>
+      </x:c>
     </x:row>
     <x:row r="92" ht="38.099998474121094" customHeight="1">
-      <x:c r="A92" s="20"/>
-      <x:c r="B92" s="21"/>
+      <x:c r="A92" s="20" t="str">
+        <x:v>EVT_W1_GAME_START</x:v>
+      </x:c>
+      <x:c r="B92" s="21" t="str">
+        <x:v>N08</x:v>
+      </x:c>
       <x:c r="C92" s="21"/>
-      <x:c r="D92" s="21"/>
-      <x:c r="E92" s="21"/>
-      <x:c r="F92" s="21"/>
-      <x:c r="G92" s="21"/>
-      <x:c r="H92" s="21"/>
-      <x:c r="I92" s="21"/>
-      <x:c r="J92" s="21"/>
-      <x:c r="K92" s="21"/>
+      <x:c r="D92" s="21" t="str">
+        <x:v>다시 눈을 뜨다</x:v>
+      </x:c>
+      <x:c r="E92" s="21" t="str">
+        <x:v>가장 친했던 동료의 변화에서 시간 공백을 체감한다.</x:v>
+      </x:c>
+      <x:c r="F92" s="21" t="str">
+        <x:v>벤자민이 제이의 상태를 확인하고, 제이는 자신이 10년을 건너뛰었다는 사실을 처음 받아들인다.</x:v>
+      </x:c>
+      <x:c r="G92" s="21" t="str">
+        <x:v>NARRATIVE</x:v>
+      </x:c>
+      <x:c r="H92" s="21" t="str">
+        <x:v>NARRATION</x:v>
+      </x:c>
+      <x:c r="I92" s="21" t="str">
+        <x:v>NARRATOR</x:v>
+      </x:c>
+      <x:c r="J92" s="21" t="str">
+        <x:v>그는 '살았다'는 말을 조금 늦게 끝냈다.
+벤자민은 캡슐 밖으로 나가는 길을 열어 준다.
+“사람부터 만나. 설명은 한 번에 들으면 머리만 아파.”
+잠깐 뒤, 수송선 쪽을 보며 덧붙인다.
+“그리고 네가 기억하는 배는… 지금 보면 좀 놀랄 거다.”</x:v>
+      </x:c>
+      <x:c r="K92" s="21" t="str">
+        <x:v>밖으로 나간다.</x:v>
+      </x:c>
       <x:c r="L92" s="21"/>
-      <x:c r="M92" s="21"/>
-      <x:c r="N92" s="21"/>
-      <x:c r="O92" s="21"/>
-      <x:c r="P92" s="21"/>
-      <x:c r="Q92" s="21"/>
+      <x:c r="M92" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N92" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O92" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P92" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Q92" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="R92" s="21"/>
       <x:c r="S92" s="21"/>
       <x:c r="T92" s="21"/>
       <x:c r="U92" s="21"/>
       <x:c r="V92" s="21"/>
       <x:c r="W92" s="21"/>
-      <x:c r="X92" s="28"/>
+      <x:c r="X92" s="28" t="str">
+        <x:v>STA_W1_MET_BENJAMIN</x:v>
+      </x:c>
+      <x:c r="Y92" t="str">
+        <x:v>SET TRUE</x:v>
+      </x:c>
+      <x:c r="Z92" t="str">
+        <x:v>STA_W1_REUNION_COUNT</x:v>
+      </x:c>
+      <x:c r="AA92" t="str">
+        <x:v>ADD 1</x:v>
+      </x:c>
+      <x:c r="AB92"/>
+      <x:c r="AC92"/>
+      <x:c r="AD92"/>
+      <x:c r="AE92"/>
+      <x:c r="AF92"/>
+      <x:c r="AG92"/>
+      <x:c r="AH92"/>
+      <x:c r="AI92"/>
+      <x:c r="AJ92"/>
+      <x:c r="AK92"/>
+      <x:c r="AL92"/>
+      <x:c r="AM92"/>
+      <x:c r="AN92"/>
+      <x:c r="AO92"/>
+      <x:c r="AP92"/>
+      <x:c r="AQ92"/>
+      <x:c r="AR92"/>
+      <x:c r="AS92"/>
+      <x:c r="AT92" s="268" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AU92" t="str">
+        <x:v>D1 Narrative v1.8: 짧은 턴이 아래로 이어지는 오프닝. 설정을 한 번에 설명하지 않음.</x:v>
+      </x:c>
     </x:row>
     <x:row r="93" ht="38.099998474121094" customHeight="1">
       <x:c r="A93" s="20"/>
